--- a/output/2026-09-03_21_Italia_Basilicata_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-09-03_21_Italia_Basilicata_Impiantistica_aspirazione_industriale.xlsx
@@ -484,10 +484,9 @@
           <t>0975 354253</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Azienda elettromeccanica attiva dal 1990 a Viggiano (PZ), zona industriale. Tratta commercializzazione/vendita di sistemi di aspirazione segatura e trucioli per lavorazione legno/metallo/PVC, oltre a impianti elettrici industriali, aria compressa, gruppi elettrogeni e assistenza apparecchiature industriali. Verificata su sito ufficiale, PagineGialle, Europages, Assodimi.</t>
+          <t>Azienda elettromeccanica attiva dal 1990 a Viggiano (PZ), zona industriale. Tratta commercializzazione/vendita di sistemi di aspirazione segatura e trucioli per lavorazione legno/metallo/PVC, oltre a impianti elettrici industriali, aria compressa, gruppi elettrogeni e assistenza apparecchiature industriali. Verificata su sito ufficiale, PagineGialle, Europages, Assodimi. [DUPLICATO — vedi anche: 2026-09-03_19_Italia_Basilicata_ATEX_Equipment-Services.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -522,10 +521,9 @@
           <t>329 24 29 565</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sede a Tito (PZ), Zona PIP. Vendita all'ingrosso di aspiratori industriali (es. mod. TTXV mono/trifase) e macchine per pulizia industriale/professionale, rivolta ad autolavaggi, officine meccaniche, carrozzerie e imprese di pulizia. Operativa su Val di Diano e bassa Campania oltre che Basilicata.</t>
+          <t>Sede a Tito (PZ), Zona PIP. Vendita all'ingrosso di aspiratori industriali (es. mod. TTXV mono/trifase) e macchine per pulizia industriale/professionale, rivolta ad autolavaggi, officine meccaniche, carrozzerie e imprese di pulizia. Operativa su Val di Diano e bassa Campania oltre che Basilicata. [DUPLICATO — vedi anche: 2026-09-03_17_Italia_Basilicata_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -560,10 +558,9 @@
           <t>392 9823056 / 0835 264263</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sede in Contrada Serra Paducci, Zona Commerciale 2, Matera. Rivenditore di aspiratori industriali e macchine per pulizia industriale di marchi terzi (IPC Portotecnica, IPC Gansow, ELSEA Aspiratori, Biemmedue), con distribuzione su Basilicata e Puglia. Oltre 30 anni di esperienza dei titolari.</t>
+          <t>Sede in Contrada Serra Paducci, Zona Commerciale 2, Matera. Rivenditore di aspiratori industriali e macchine per pulizia industriale di marchi terzi (IPC Portotecnica, IPC Gansow, ELSEA Aspiratori, Biemmedue), con distribuzione su Basilicata e Puglia. Oltre 30 anni di esperienza dei titolari. [DUPLICATO — vedi anche: 2026-09-03_17_Italia_Basilicata_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -605,7 +602,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sede legale in Vico Nazionale Nord, Grottole (MT), P.IVA 00595080771. Vendita e assistenza pre/post-vendita di aspiratori professionali industriali (anche aspirazione liquidi), idropulitrici, lavapavimenti, spazzatrici, per settori industriali e officine.</t>
+          <t>Sede legale in Vico Nazionale Nord, Grottole (MT), P.IVA 00595080771. Vendita e assistenza pre/post-vendita di aspiratori professionali industriali (anche aspirazione liquidi), idropulitrici, lavapavimenti, spazzatrici, per settori industriali e officine. [DUPLICATO — vedi anche: 2026-09-03_17_Italia_Basilicata_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
